--- a/other/documents/QAPP/baseline_wqx_coordinator_tasks.xlsx
+++ b/other/documents/QAPP/baseline_wqx_coordinator_tasks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t>Frequency</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Responsible Person</t>
   </si>
   <si>
-    <t>Water Quality Coordinator</t>
-  </si>
-  <si>
     <t>Transfer field samples to laboratories</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>Review QAPP and overall project design</t>
   </si>
   <si>
-    <t>Committee</t>
-  </si>
-  <si>
     <t>38, 39</t>
   </si>
   <si>
@@ -120,7 +114,19 @@
     <t>Confirm laboratory schedules and capabilities</t>
   </si>
   <si>
-    <t>Review data for five-year trends in the context of regulatory values</t>
+    <t>Review previous year's data for five-year trends in the context of regulatory values</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Project Manager / Project QA Officer</t>
+  </si>
+  <si>
+    <t>Committee Members</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -160,7 +166,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -168,26 +174,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,237 +703,273 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
-    <col min="5" max="5" width="68.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>19</v>
+      <c r="A1" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:6" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="20">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="20">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="20">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="20">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="20">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="19"/>
+    </row>
+    <row r="14" spans="1:6" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B14" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="4">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="F14" s="24">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="4">
-        <v>39</v>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A5:F15">
+    <sortCondition ref="A5:A15"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
